--- a/data/trans_orig/IP2907_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP2907_2023-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9197</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21114</t>
+          <t>21251</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>14389</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28959</t>
+          <t>28759</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25968</t>
+          <t>26204</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44490</t>
+          <t>45228</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,98%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50286</t>
+          <t>50149</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62203</t>
+          <t>62194</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45648</t>
+          <t>45848</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60504</t>
+          <t>60218</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101517</t>
+          <t>100779</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>120039</t>
+          <t>119803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,05%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10709</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22234</t>
+          <t>23340</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15936</t>
+          <t>16074</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33233</t>
+          <t>33477</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29943</t>
+          <t>29954</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51403</t>
+          <t>51139</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,25%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74041</t>
+          <t>72935</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>85566</t>
+          <t>85238</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90437</t>
+          <t>90193</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107734</t>
+          <t>107596</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>168542</t>
+          <t>168806</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>190002</t>
+          <t>189991</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,38%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8441</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17922</t>
+          <t>17870</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9524</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19865</t>
+          <t>20239</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19219</t>
+          <t>19440</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34484</t>
+          <t>34557</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,95%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38077</t>
+          <t>38129</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47558</t>
+          <t>47775</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43492</t>
+          <t>43118</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53833</t>
+          <t>53858</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84871</t>
+          <t>84798</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>100136</t>
+          <t>99915</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,11%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,71%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11971</t>
+          <t>11385</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24815</t>
+          <t>24775</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9558</t>
+          <t>8619</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29235</t>
+          <t>27801</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25648</t>
+          <t>25642</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48194</t>
+          <t>48150</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,99%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>42972</t>
+          <t>43012</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>55816</t>
+          <t>56402</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>44634</t>
+          <t>46068</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>64311</t>
+          <t>65250</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93463</t>
+          <t>93507</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116009</t>
+          <t>116015</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,9%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6160</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13621</t>
+          <t>13611</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8134</t>
+          <t>8102</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17222</t>
+          <t>16776</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16678</t>
+          <t>17048</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28064</t>
+          <t>28722</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>38,34%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>20589</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28040</t>
+          <t>28029</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23497</t>
+          <t>23943</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32585</t>
+          <t>32617</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46855</t>
+          <t>46197</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58241</t>
+          <t>57871</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>61,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,25%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2435</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9378</t>
+          <t>8706</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11071</t>
+          <t>11639</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7589</t>
+          <t>7944</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16850</t>
+          <t>17271</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33411</t>
+          <t>34083</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40354</t>
+          <t>40417</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42711</t>
+          <t>42143</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49816</t>
+          <t>49818</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>79721</t>
+          <t>79300</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88982</t>
+          <t>88627</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20427</t>
+          <t>20373</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37543</t>
+          <t>36477</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21370</t>
+          <t>21271</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50632</t>
+          <t>48849</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46675</t>
+          <t>46802</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78735</t>
+          <t>80397</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,25%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>83547</t>
+          <t>84613</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>100663</t>
+          <t>100717</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103139</t>
+          <t>104922</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>132401</t>
+          <t>132500</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>196126</t>
+          <t>194464</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>228186</t>
+          <t>228059</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,97%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8772</t>
+          <t>8507</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20697</t>
+          <t>20335</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11224</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>24982</t>
+          <t>25840</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22615</t>
+          <t>22606</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40620</t>
+          <t>41710</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3221,7 +3221,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>106771</t>
+          <t>107133</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>118696</t>
+          <t>118961</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>128523</t>
+          <t>127665</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>142281</t>
+          <t>142284</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>240354</t>
+          <t>239264</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>258359</t>
+          <t>258368</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>100877</t>
+          <t>100103</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>132963</t>
+          <t>135554</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>125043</t>
+          <t>126570</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>172695</t>
+          <t>171111</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>237069</t>
+          <t>236214</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>295702</t>
+          <t>290681</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>484046</t>
+          <t>481455</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>516132</t>
+          <t>516906</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>564585</t>
+          <t>566169</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>612237</t>
+          <t>610710</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1058587</t>
+          <t>1063608</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1117220</t>
+          <t>1118075</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,56%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2907_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP2907_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17672</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12236</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23888</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>29,33%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>20,3%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,64%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>14477</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9206</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21251</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20,28%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20588</t>
+          <t>12703</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14389</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28759</t>
+          <t>17884</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>35065</t>
+          <t>30376</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26204</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45228</t>
+          <t>37980</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42591</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>36375</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>48027</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>70,67%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>60,36%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>79,7%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>56923</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50149</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>62194</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>79,72%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>70,24%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54019</t>
+          <t>42219</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45848</t>
+          <t>37038</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60218</t>
+          <t>46644</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>110942</t>
+          <t>84810</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100779</t>
+          <t>77206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>119803</t>
+          <t>92486</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>80,29%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>20769</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13924</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>30026</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18,47%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,39%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>26,71%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>16248</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11037</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>23340</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>16,88%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,24%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23045</t>
+          <t>16616</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16074</t>
+          <t>10978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33477</t>
+          <t>22944</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>39293</t>
+          <t>37386</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29954</t>
+          <t>27838</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51139</t>
+          <t>47420</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>91654</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>82397</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>98499</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>73,29%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,61%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>80027</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>72935</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>85238</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>83,12%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,76%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>88,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>100625</t>
+          <t>77472</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>90193</t>
+          <t>71144</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>107596</t>
+          <t>83110</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>180652</t>
+          <t>169126</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>168806</t>
+          <t>159092</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>189991</t>
+          <t>178674</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,52%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>112423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>112423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>96275</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>96275</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>96275</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>123670</t>
+          <t>94088</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>123670</t>
+          <t>94088</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>123670</t>
+          <t>94088</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>219945</t>
+          <t>206512</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>219945</t>
+          <t>206512</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>219945</t>
+          <t>206512</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12667</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7964</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17611</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>22,59%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,2%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>31,4%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12537</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8224</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>17870</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>22,39%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>31,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14249</t>
+          <t>12041</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9499</t>
+          <t>7972</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20239</t>
+          <t>17598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>26786</t>
+          <t>24708</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19440</t>
+          <t>18857</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34557</t>
+          <t>32406</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>43415</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>38471</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>48118</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>77,41%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>68,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>85,8%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>43462</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>38129</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>47775</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>77,61%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>68,09%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,31%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49108</t>
+          <t>42497</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>43118</t>
+          <t>36940</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53858</t>
+          <t>46566</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,06%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>92569</t>
+          <t>85912</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84798</t>
+          <t>78214</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>99915</t>
+          <t>91763</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>70,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>82,95%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>56082</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>56082</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>56082</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55999</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55999</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55999</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63357</t>
+          <t>54538</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63357</t>
+          <t>54538</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>63357</t>
+          <t>54538</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>119355</t>
+          <t>110620</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>119355</t>
+          <t>110620</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>119355</t>
+          <t>110620</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>16878</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8862</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>26096</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12,96%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>38,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>17916</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11385</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>24775</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>26,43%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36,55%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18358</t>
+          <t>17149</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8619</t>
+          <t>11045</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27801</t>
+          <t>24058</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>36274</t>
+          <t>34028</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25642</t>
+          <t>24345</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48150</t>
+          <t>44733</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>32,7%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>51506</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>42288</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>59522</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>75,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61,84%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>87,04%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>49871</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>43012</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>56402</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>73,57%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>63,45%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>83,2%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>55511</t>
+          <t>51275</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>46068</t>
+          <t>44366</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65250</t>
+          <t>57379</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>105383</t>
+          <t>102780</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>93507</t>
+          <t>92075</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>116015</t>
+          <t>112463</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>67,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>82,2%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>68384</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>68384</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>68384</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>67787</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>67787</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>67787</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73869</t>
+          <t>68424</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>73869</t>
+          <t>68424</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73869</t>
+          <t>68424</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>141657</t>
+          <t>136808</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>141657</t>
+          <t>136808</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>141657</t>
+          <t>136808</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12472</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8218</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>17112</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>31,51%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>20,76%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>43,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>9781</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>6171</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13611</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>28,6%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18,04%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>39,8%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12244</t>
+          <t>10142</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8102</t>
+          <t>6192</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16776</t>
+          <t>14242</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22025</t>
+          <t>22613</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17048</t>
+          <t>16472</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28722</t>
+          <t>28818</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>27107</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>22467</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>31361</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>68,49%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>56,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>79,24%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>24419</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>20589</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>28029</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>71,4%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>60,2%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>81,96%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>28475</t>
+          <t>25228</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23943</t>
+          <t>21128</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32617</t>
+          <t>29178</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>52894</t>
+          <t>52336</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46197</t>
+          <t>46131</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57871</t>
+          <t>58477</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>78,02%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>5686</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3039</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>9437</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>12,04%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>19,99%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>4992</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2372</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8706</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>11,67%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>20,35%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6895</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>2278</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11639</t>
+          <t>8559</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>10598</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>6872</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17271</t>
+          <t>16247</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>41523</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>37772</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>44170</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>87,96%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>80,01%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>93,56%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>37797</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>34083</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>40417</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>88,33%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>79,65%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>94,46%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>46887</t>
+          <t>37868</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42143</t>
+          <t>34221</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49818</t>
+          <t>40502</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>88,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>84684</t>
+          <t>79391</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>79300</t>
+          <t>73742</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88627</t>
+          <t>83117</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>92,36%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>42789</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>42789</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>42789</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>42780</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>42780</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>42780</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>96571</t>
+          <t>89989</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>96571</t>
+          <t>89989</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>96571</t>
+          <t>89989</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>27551</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>18940</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>40580</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>19,78%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>13,6%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>29,13%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>27927</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>20373</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>36477</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>23,06%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>16,82%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>30,12%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>32984</t>
+          <t>28457</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21271</t>
+          <t>21332</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48849</t>
+          <t>36756</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>60910</t>
+          <t>56009</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46802</t>
+          <t>44481</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>80397</t>
+          <t>70346</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>111751</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>98722</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>120362</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>80,22%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>70,87%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>86,4%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>93163</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>84613</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>100717</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>76,94%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>69,88%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>83,18%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>144</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>120787</t>
+          <t>90515</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>104922</t>
+          <t>82216</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>132500</t>
+          <t>97640</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>213951</t>
+          <t>202265</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>194464</t>
+          <t>187928</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>228059</t>
+          <t>213793</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,78%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>139302</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>139302</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>139302</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>121090</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>121090</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>121090</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>153771</t>
+          <t>118972</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>153771</t>
+          <t>118972</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>153771</t>
+          <t>118972</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>274861</t>
+          <t>258274</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>274861</t>
+          <t>258274</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>274861</t>
+          <t>258274</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>17054</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>10704</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>25562</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>10,91%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>16,35%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>13548</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>8507</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>20335</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>10,63%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>15,95%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>17544</t>
+          <t>14183</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25840</t>
+          <t>20819</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>31092</t>
+          <t>31237</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22606</t>
+          <t>23191</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>41710</t>
+          <t>41503</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>139284</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>130776</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>145634</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>89,09%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>83,65%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>93,15%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>113920</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>107133</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>118961</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>89,37%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>84,05%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>93,33%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>135961</t>
+          <t>121823</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>127665</t>
+          <t>115187</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>142284</t>
+          <t>127345</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>249882</t>
+          <t>261107</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>239264</t>
+          <t>250841</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>258368</t>
+          <t>269153</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>156338</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>156338</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>156338</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>127468</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>127468</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>127468</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>153505</t>
+          <t>136006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>153505</t>
+          <t>136006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>153505</t>
+          <t>136006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>280974</t>
+          <t>292344</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>280974</t>
+          <t>292344</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>280974</t>
+          <t>292344</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>130749</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>111678</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>150256</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>19,24%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>16,43%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>22,11%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>117425</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>100103</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>135554</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>19,03%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>16,22%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>21,97%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>145907</t>
+          <t>116205</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>126570</t>
+          <t>101842</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>171111</t>
+          <t>133829</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>263332</t>
+          <t>246954</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>236214</t>
+          <t>223274</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>290681</t>
+          <t>276884</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>548832</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>529325</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>567903</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>80,76%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>77,89%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>83,57%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>726</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>499584</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>481455</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>516906</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>80,97%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>78,03%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>83,78%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>750</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>591373</t>
+          <t>488895</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>566169</t>
+          <t>471271</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>610710</t>
+          <t>503258</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,79%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1090957</t>
+          <t>1037727</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1063608</t>
+          <t>1007797</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1118075</t>
+          <t>1061407</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>80,56%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,62%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>679581</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>679581</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>679581</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>904</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>617009</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>617009</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>617009</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>737280</t>
+          <t>605100</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>737280</t>
+          <t>605100</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>737280</t>
+          <t>605100</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1354289</t>
+          <t>1284681</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1354289</t>
+          <t>1284681</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1354289</t>
+          <t>1284681</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
